--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -3374,13 +3374,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31260979-0040-40DC-AB2D-9F8BE42B6F96}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6EE466EC-6534-40DD-B0B3-920D5B78DCBC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EC18153-1F3A-4DA5-91E9-AC2CBFB64E30}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24A30C35-7CDF-4D14-A217-8B885126B6A9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D64B65C0-72D9-4C20-92AA-2978A7C2055D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C269FB4C-C3CA-4AD2-915A-E24B10FF7268}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -3374,13 +3374,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6EE466EC-6534-40DD-B0B3-920D5B78DCBC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8387B09-AD8F-4739-A3BF-FB6DAEB1A1DD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24A30C35-7CDF-4D14-A217-8B885126B6A9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3954BC88-340B-49EA-A03D-25A3BAC959C8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C269FB4C-C3CA-4AD2-915A-E24B10FF7268}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{474A7F06-CAF6-4AC7-86F3-2AF35FCDC154}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -3374,13 +3374,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8387B09-AD8F-4739-A3BF-FB6DAEB1A1DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27F7B353-955C-4244-9740-13C49AA46C35}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3954BC88-340B-49EA-A03D-25A3BAC959C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F78A5BC-EAC9-4E59-80DC-930BFB35E452}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{474A7F06-CAF6-4AC7-86F3-2AF35FCDC154}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7D84FDB-768C-4291-9D86-A529794C2797}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -3374,13 +3374,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27F7B353-955C-4244-9740-13C49AA46C35}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA93D810-1D38-4A59-A7A7-54F75244C9FB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F78A5BC-EAC9-4E59-80DC-930BFB35E452}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7B53642-CBC6-47D2-9280-C67B9FBB0D73}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7D84FDB-768C-4291-9D86-A529794C2797}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D798F76-D662-4B9B-A2C8-ECA620F34D9C}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2884,13 +2884,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F01CD711-ACFC-4E95-B80E-BECC55DD3E2A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9E2FDD4-BBAB-4F89-9E0D-CDFB76C03DF7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA91DF83-5106-446F-B2D5-B0D74DB54B22}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D056C57-0503-4B83-938B-3FD1EDFA2A1D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6EDAEC7-F021-4F1D-852F-E28FBD27E116}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B95B7F90-51D5-4D6E-9FE1-76759257D9F9}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2884,13 +2884,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9E2FDD4-BBAB-4F89-9E0D-CDFB76C03DF7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{823A824A-DED8-4E65-B048-9F91F9C1B83F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D056C57-0503-4B83-938B-3FD1EDFA2A1D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A32C85A-F260-4020-9567-B6E60A060E11}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B95B7F90-51D5-4D6E-9FE1-76759257D9F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66F30507-37D7-47A3-AF04-65F6373D10F5}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2606,291 +2606,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{823A824A-DED8-4E65-B048-9F91F9C1B83F}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A32C85A-F260-4020-9567-B6E60A060E11}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66F30507-37D7-47A3-AF04-65F6373D10F5}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2606,4 +2606,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{661E654B-23AE-4F29-B08F-45C9309DEDF9}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A94DD8E-B443-4F8F-BC9D-617541288474}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCDDF8B0-9CF4-49C7-9FDD-09B3183DDC7B}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2606,291 +2606,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{661E654B-23AE-4F29-B08F-45C9309DEDF9}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A94DD8E-B443-4F8F-BC9D-617541288474}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCDDF8B0-9CF4-49C7-9FDD-09B3183DDC7B}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2606,4 +2606,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9202A925-0ECD-4D91-8BC6-1521A32D09E0}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52A81C5B-794A-44BF-BB4F-A4393DF81024}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E4D99AB-1D4E-4FC3-B152-F8B23800EA89}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2884,13 +2884,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9202A925-0ECD-4D91-8BC6-1521A32D09E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CE21D6C-9620-4389-AD47-4D57BAF2EDE7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52A81C5B-794A-44BF-BB4F-A4393DF81024}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0E2A234-AF21-4F80-B370-44CB2294D8D6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E4D99AB-1D4E-4FC3-B152-F8B23800EA89}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDE53788-25DF-44B0-BE37-6AFB2D1B8112}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2884,13 +2884,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CE21D6C-9620-4389-AD47-4D57BAF2EDE7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2FC3CFF-74B5-4845-A7F8-FFA9BC8D8FAA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0E2A234-AF21-4F80-B370-44CB2294D8D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBE2D979-8BFE-42CD-BF2A-E39E731A77B9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDE53788-25DF-44B0-BE37-6AFB2D1B8112}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FA83327-EFD5-45D4-B792-52C0A6E1EBE9}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2884,13 +2884,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2FC3CFF-74B5-4845-A7F8-FFA9BC8D8FAA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27EFCF2B-D0E9-49F2-8B86-C3E81F302FB8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBE2D979-8BFE-42CD-BF2A-E39E731A77B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{884A9FA9-EACC-42B3-9B1D-89EF3B813BDB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FA83327-EFD5-45D4-B792-52C0A6E1EBE9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECA8E366-A462-4896-9ECB-31C0DFA60202}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2884,13 +2884,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27EFCF2B-D0E9-49F2-8B86-C3E81F302FB8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF5781E-08F2-4DFA-BD04-8676D3292638}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{884A9FA9-EACC-42B3-9B1D-89EF3B813BDB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34BB3596-A6D9-41FF-A820-3A1D82B2B0F8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECA8E366-A462-4896-9ECB-31C0DFA60202}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48844871-6BAC-4243-BA25-F1255A028D67}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2884,13 +2884,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF5781E-08F2-4DFA-BD04-8676D3292638}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA175AE1-D3CD-403A-9592-5C1C4DFEE1B2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34BB3596-A6D9-41FF-A820-3A1D82B2B0F8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41781FDF-9FFC-4161-8CF7-C39CE85CD090}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48844871-6BAC-4243-BA25-F1255A028D67}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93B6FB04-DB46-4A9C-B2CC-CB43FC00F1EE}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2606,291 +2606,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA175AE1-D3CD-403A-9592-5C1C4DFEE1B2}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41781FDF-9FFC-4161-8CF7-C39CE85CD090}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93B6FB04-DB46-4A9C-B2CC-CB43FC00F1EE}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2606,4 +2606,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7A8513C-2881-40C5-9D49-F8C668010FC2}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30322070-F43B-45B1-B5EC-E807A8FFB798}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FF7EF5D-25DC-4A79-AF54-05203A39DE51}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2371,7 +2371,7 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B70" t="s">
         <v>88</v>
@@ -2884,13 +2884,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7A8513C-2881-40C5-9D49-F8C668010FC2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C6C2BA8-82AA-41E1-A380-5415AADB0A55}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30322070-F43B-45B1-B5EC-E807A8FFB798}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E4D01E3-7A63-4858-88FF-E63A1CD68D10}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FF7EF5D-25DC-4A79-AF54-05203A39DE51}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79175ACB-9761-443D-B40E-3D88E628E4D0}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2884,13 +2884,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C6C2BA8-82AA-41E1-A380-5415AADB0A55}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0F87A64-0F43-4475-9482-3A2C7E897C92}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E4D01E3-7A63-4858-88FF-E63A1CD68D10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42B85789-2448-426A-A658-9F2854E94DE7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79175ACB-9761-443D-B40E-3D88E628E4D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10DF1CEC-F81B-45AC-82F0-342D398A15B4}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2884,13 +2884,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0F87A64-0F43-4475-9482-3A2C7E897C92}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6487ECEE-3160-46B6-BE1D-68AA7B66EC88}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42B85789-2448-426A-A658-9F2854E94DE7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7845B52-DC0F-457D-BAE2-00085BCD00CF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10DF1CEC-F81B-45AC-82F0-342D398A15B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD9219D8-8251-4A15-8EC2-C09278A986B6}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2884,13 +2884,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6487ECEE-3160-46B6-BE1D-68AA7B66EC88}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14067BE3-B3CB-4C9D-9F73-994825F2DCCF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7845B52-DC0F-457D-BAE2-00085BCD00CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F69626E-254E-4362-9606-38C825CC7CC6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD9219D8-8251-4A15-8EC2-C09278A986B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA950850-1324-4EB8-905B-E3A3A46ABB1F}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2884,13 +2884,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14067BE3-B3CB-4C9D-9F73-994825F2DCCF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21481584-1796-43F3-BBF0-AD036A18C1A5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F69626E-254E-4362-9606-38C825CC7CC6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB917B63-C2A4-4095-9AE8-43552BA22930}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA950850-1324-4EB8-905B-E3A3A46ABB1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AECD20F0-00EA-405E-9005-04168D66FCE7}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="98">
   <si>
     <t>species_sci</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>Sus scrofa</t>
+  </si>
+  <si>
+    <t>Sus scrofa domesticus</t>
   </si>
   <si>
     <t>Sus scrofa domestica</t>
@@ -2371,10 +2374,10 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B70" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C70">
         <v>44.5945945945946</v>
@@ -2397,10 +2400,10 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B71" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C71">
         <v>62.5242718446602</v>
@@ -2423,10 +2426,10 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B72" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C72">
         <v>55</v>
@@ -2449,10 +2452,10 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B73" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C73">
         <v>72.5714285714286</v>
@@ -2475,10 +2478,10 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B74" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C74">
         <v>55.2736842105263</v>
@@ -2501,10 +2504,10 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C75">
         <v>36.5486725663717</v>
@@ -2527,10 +2530,10 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B76" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C76">
         <v>71.2</v>
@@ -2553,10 +2556,10 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B77" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C77">
         <v>66.4655172413793</v>
@@ -2579,10 +2582,10 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B78" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C78">
         <v>61.4814814814815</v>
@@ -2606,291 +2609,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21481584-1796-43F3-BBF0-AD036A18C1A5}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB917B63-C2A4-4095-9AE8-43552BA22930}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AECD20F0-00EA-405E-9005-04168D66FCE7}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2609,4 +2609,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1977A36-C5BD-4E82-A001-CF6C4C69FFBD}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90524941-4F93-449A-AD23-6A38556485DB}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F152A7AB-C1F9-4D78-9789-44A091DDD371}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2609,291 +2609,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1977A36-C5BD-4E82-A001-CF6C4C69FFBD}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90524941-4F93-449A-AD23-6A38556485DB}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F152A7AB-C1F9-4D78-9789-44A091DDD371}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2609,4 +2609,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42597A69-57A3-46AD-9F49-EA8D31DBD268}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85ED2E7D-490B-4C17-9DB3-223694B01999}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9FA243D6-1E89-4E64-A66D-30E0DD53DF60}"/>
 </file>
--- a/____EvoM1_TraitTable/gait_excursion_medina.xlsx
+++ b/____EvoM1_TraitTable/gait_excursion_medina.xlsx
@@ -2609,4 +2609,291 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE84605A-A8D9-49D2-A1CE-313D95A9DA3E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C103DF0-6853-43A6-8441-26228366762F}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A81E1ABF-BD4D-44F8-86AA-5746D59968DA}"/>
 </file>